--- a/webapp/backend/template/krc_초기정기_template.xlsx
+++ b/webapp/backend/template/krc_초기정기_template.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="주요공정별 위험성평가 작성예시" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="주요공정별 위험성평가 작성예시" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -912,7 +912,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R15"/>
+  <dimension ref="A1:R19"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.75" defaultRowHeight="16.5"/>
   <cols>
     <col width="14.75" customWidth="1" style="1" min="1" max="3"/>
@@ -1208,7 +1208,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="75.2" customHeight="1" s="30">
+    <row r="10" ht="45" customHeight="1" s="30">
       <c r="A10" s="7" t="n"/>
       <c r="B10" s="7" t="n"/>
       <c r="C10" s="8" t="n"/>
@@ -1228,7 +1228,7 @@
       <c r="Q10" s="31" t="n"/>
       <c r="R10" s="7" t="n"/>
     </row>
-    <row r="11" ht="75.2" customHeight="1" s="30">
+    <row r="11" ht="45" customHeight="1" s="30">
       <c r="A11" s="4" t="n"/>
       <c r="B11" s="38" t="n"/>
       <c r="C11" s="41" t="n"/>
@@ -1248,7 +1248,7 @@
       <c r="Q11" s="31" t="n"/>
       <c r="R11" s="7" t="n"/>
     </row>
-    <row r="12" ht="75.2" customHeight="1" s="30">
+    <row r="12" ht="45" customHeight="1" s="30">
       <c r="A12" s="7" t="n"/>
       <c r="B12" s="7" t="n"/>
       <c r="C12" s="8" t="n"/>
@@ -1268,7 +1268,7 @@
       <c r="Q12" s="31" t="n"/>
       <c r="R12" s="7" t="n"/>
     </row>
-    <row r="13" ht="75.2" customHeight="1" s="30">
+    <row r="13" ht="45" customHeight="1" s="30">
       <c r="A13" s="4" t="n"/>
       <c r="B13" s="38" t="n"/>
       <c r="C13" s="41" t="n"/>
@@ -1288,7 +1288,7 @@
       <c r="Q13" s="31" t="n"/>
       <c r="R13" s="7" t="n"/>
     </row>
-    <row r="14" ht="75.2" customHeight="1" s="30">
+    <row r="14" ht="45" customHeight="1" s="30">
       <c r="A14" s="7" t="n"/>
       <c r="B14" s="7" t="n"/>
       <c r="C14" s="8" t="n"/>
@@ -1308,7 +1308,7 @@
       <c r="Q14" s="31" t="n"/>
       <c r="R14" s="7" t="n"/>
     </row>
-    <row r="15" ht="75.2" customHeight="1" s="30">
+    <row r="15" ht="45" customHeight="1" s="30">
       <c r="A15" s="4" t="n"/>
       <c r="B15" s="38" t="n"/>
       <c r="C15" s="41" t="n"/>
@@ -1328,22 +1328,108 @@
       <c r="Q15" s="31" t="n"/>
       <c r="R15" s="7" t="n"/>
     </row>
+    <row r="16" ht="45" customHeight="1" s="30">
+      <c r="A16" s="7" t="n"/>
+      <c r="B16" s="7" t="n"/>
+      <c r="C16" s="8" t="n"/>
+      <c r="D16" s="33" t="n"/>
+      <c r="E16" s="34" t="n"/>
+      <c r="F16" s="4" t="n"/>
+      <c r="G16" s="4" t="n"/>
+      <c r="H16" s="4" t="n"/>
+      <c r="I16" s="7" t="n"/>
+      <c r="J16" s="7" t="n"/>
+      <c r="K16" s="33" t="n"/>
+      <c r="L16" s="33" t="n"/>
+      <c r="M16" s="33" t="n"/>
+      <c r="N16" s="33" t="n"/>
+      <c r="O16" s="34" t="n"/>
+      <c r="P16" s="7" t="n"/>
+      <c r="Q16" s="31" t="n"/>
+      <c r="R16" s="7" t="n"/>
+    </row>
+    <row r="17" ht="45" customHeight="1" s="30">
+      <c r="A17" s="4" t="n"/>
+      <c r="B17" s="38" t="n"/>
+      <c r="C17" s="41" t="n"/>
+      <c r="D17" s="42" t="n"/>
+      <c r="E17" s="40" t="n"/>
+      <c r="F17" s="38" t="n"/>
+      <c r="G17" s="38" t="n"/>
+      <c r="H17" s="38" t="n"/>
+      <c r="I17" s="38" t="n"/>
+      <c r="J17" s="41" t="n"/>
+      <c r="K17" s="42" t="n"/>
+      <c r="L17" s="42" t="n"/>
+      <c r="M17" s="42" t="n"/>
+      <c r="N17" s="42" t="n"/>
+      <c r="O17" s="40" t="n"/>
+      <c r="P17" s="4" t="n"/>
+      <c r="Q17" s="31" t="n"/>
+      <c r="R17" s="7" t="n"/>
+    </row>
+    <row r="18" ht="45" customHeight="1" s="30">
+      <c r="A18" s="7" t="n"/>
+      <c r="B18" s="7" t="n"/>
+      <c r="C18" s="8" t="n"/>
+      <c r="D18" s="33" t="n"/>
+      <c r="E18" s="34" t="n"/>
+      <c r="F18" s="4" t="n"/>
+      <c r="G18" s="4" t="n"/>
+      <c r="H18" s="4" t="n"/>
+      <c r="I18" s="7" t="n"/>
+      <c r="J18" s="7" t="n"/>
+      <c r="K18" s="33" t="n"/>
+      <c r="L18" s="33" t="n"/>
+      <c r="M18" s="33" t="n"/>
+      <c r="N18" s="33" t="n"/>
+      <c r="O18" s="34" t="n"/>
+      <c r="P18" s="7" t="n"/>
+      <c r="Q18" s="31" t="n"/>
+      <c r="R18" s="7" t="n"/>
+    </row>
+    <row r="19" ht="45" customHeight="1" s="30">
+      <c r="A19" s="4" t="n"/>
+      <c r="B19" s="38" t="n"/>
+      <c r="C19" s="41" t="n"/>
+      <c r="D19" s="42" t="n"/>
+      <c r="E19" s="40" t="n"/>
+      <c r="F19" s="38" t="n"/>
+      <c r="G19" s="38" t="n"/>
+      <c r="H19" s="38" t="n"/>
+      <c r="I19" s="38" t="n"/>
+      <c r="J19" s="41" t="n"/>
+      <c r="K19" s="42" t="n"/>
+      <c r="L19" s="42" t="n"/>
+      <c r="M19" s="42" t="n"/>
+      <c r="N19" s="42" t="n"/>
+      <c r="O19" s="40" t="n"/>
+      <c r="P19" s="4" t="n"/>
+      <c r="Q19" s="31" t="n"/>
+      <c r="R19" s="7" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="55">
+  <mergeCells count="73">
     <mergeCell ref="B12:B13"/>
     <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B18:B19"/>
     <mergeCell ref="F12:F13"/>
     <mergeCell ref="P10:Q10"/>
     <mergeCell ref="B8:B9"/>
     <mergeCell ref="J14:O15"/>
+    <mergeCell ref="I16:I17"/>
+    <mergeCell ref="F16:F17"/>
     <mergeCell ref="G8:H8"/>
     <mergeCell ref="J8:O9"/>
     <mergeCell ref="G10:G11"/>
     <mergeCell ref="B14:B15"/>
+    <mergeCell ref="F18:F19"/>
+    <mergeCell ref="P9:Q9"/>
     <mergeCell ref="J12:O13"/>
-    <mergeCell ref="P9:Q9"/>
     <mergeCell ref="N5:N6"/>
     <mergeCell ref="B2:C2"/>
+    <mergeCell ref="C18:E19"/>
+    <mergeCell ref="I18:I19"/>
     <mergeCell ref="C14:E15"/>
     <mergeCell ref="F8:F9"/>
     <mergeCell ref="I12:I13"/>
@@ -1356,22 +1442,32 @@
     <mergeCell ref="B10:B11"/>
     <mergeCell ref="B1:C1"/>
     <mergeCell ref="Q1:Q6"/>
+    <mergeCell ref="G18:G19"/>
     <mergeCell ref="G14:G15"/>
     <mergeCell ref="A5:A6"/>
     <mergeCell ref="I14:I15"/>
     <mergeCell ref="C10:E11"/>
+    <mergeCell ref="C16:E17"/>
+    <mergeCell ref="P17:Q17"/>
     <mergeCell ref="I8:I9"/>
+    <mergeCell ref="H16:H17"/>
+    <mergeCell ref="P16:Q16"/>
     <mergeCell ref="H12:H13"/>
     <mergeCell ref="L1:L6"/>
     <mergeCell ref="P13:Q13"/>
     <mergeCell ref="M2:M4"/>
+    <mergeCell ref="P19:Q19"/>
     <mergeCell ref="O5:P6"/>
+    <mergeCell ref="G16:G17"/>
     <mergeCell ref="I10:I11"/>
     <mergeCell ref="C12:E13"/>
     <mergeCell ref="F14:F15"/>
+    <mergeCell ref="H18:H19"/>
     <mergeCell ref="H14:H15"/>
     <mergeCell ref="B6:C6"/>
+    <mergeCell ref="P18:Q18"/>
     <mergeCell ref="R5:R6"/>
+    <mergeCell ref="J16:O17"/>
     <mergeCell ref="P12:Q12"/>
     <mergeCell ref="O2:P4"/>
     <mergeCell ref="D1:K6"/>
@@ -1382,6 +1478,8 @@
     <mergeCell ref="N2:N4"/>
     <mergeCell ref="C8:E9"/>
     <mergeCell ref="P14:Q14"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="J18:O19"/>
     <mergeCell ref="F10:F11"/>
     <mergeCell ref="H10:H11"/>
     <mergeCell ref="M5:M6"/>
